--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-08.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-08.xlsx
@@ -474,517 +474,517 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583987660861</v>
+        <v>5583999695161</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Humberto</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Humberto Ribeiro dos Santos</t>
+          <t>Amanda Leticia Franca da Silva</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583988304523</v>
+        <v>5583999617935</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adryellen</t>
+          <t>Ednado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Adryellen Karina Santos de Pontes</t>
+          <t>Ednado de Araujo Pereira</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583987725774</v>
+        <v>5583998818221</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>João</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jose Jorge de Araujo Correia</t>
+          <t>João Carlos Borges Correia de Aguiar</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583988453534</v>
+        <v>5583987660861</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Humberto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marcos Aurelio Reitzel</t>
+          <t>Humberto Ribeiro dos Santos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583987894010</v>
+        <v>5583988304523</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Adryellen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Antonio Dantas Hermenegildo</t>
+          <t>Adryellen Karina Santos de Pontes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583986528885</v>
+        <v>5583998032881</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Fabiano</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wellington Silva de Sousa</t>
+          <t>Fabiano Lima da Silva</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583988432660</v>
+        <v>5583987725774</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ronaldo</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ronaldo Melo Silva</t>
+          <t>Jose Jorge de Araujo Correia</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583986704170</v>
+        <v>5583988453534</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Valderlan</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Valderlan Felipe Silva de Souza</t>
+          <t>Marcos Aurelio Reitzel</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583996647757</v>
+        <v>5583987894010</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Wellington Lourenco da Silva</t>
+          <t>Antonio Dantas Hermenegildo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583987004874</v>
+        <v>5583986528885</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paulo dos Santos Marinho</t>
+          <t>Wellington Silva de Sousa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583987970344</v>
+        <v>5583988432660</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Priscila</t>
+          <t>Ronaldo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Priscila Regis Goncalves</t>
+          <t>Ronaldo Melo Silva</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583996949999</v>
+        <v>5583986704170</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jaynne</t>
+          <t>Valderlan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jaynne Mamede Sousa</t>
+          <t>Valderlan Felipe Silva de Souza</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583998886672</v>
+        <v>5583996647757</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leandro Jose Pereira de Carvalho</t>
+          <t>Jose Wellington Lourenco da Silva</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583993545964</v>
+        <v>5583987004874</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maria da Penha Nobrega da Silva</t>
+          <t>Paulo dos Santos Marinho</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5581995260009</v>
+        <v>5583987970344</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Priscila</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mariana Freire da Costa Farias</t>
+          <t>Priscila Regis Goncalves</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583988001595</v>
+        <v>5583996949999</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Valneide</t>
+          <t>Jaynne</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Valneide Macedo Lins Fialho</t>
+          <t>Jaynne Mamede Sousa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5521997714797</v>
+        <v>5583998886672</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jose Amorim</t>
+          <t>Leandro Jose Pereira de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5522981585707</v>
+        <v>5583993545964</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Diego de Souza Lourenço</t>
+          <t>Maria da Penha Nobrega da Silva</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583987982658</v>
+        <v>5581995260009</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Mariana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Maria de Fatima Nascimento de Oliveira</t>
+          <t>Mariana Freire da Costa Farias</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583988865167</v>
+        <v>5583988001595</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zaqueu</t>
+          <t>Valneide</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zaqueu Ernesto da Silva</t>
+          <t>Valneide Macedo Lins Fialho</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583996825596</v>
+        <v>5521997714797</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alex Bruno dos Santos Amaral</t>
+          <t>Jose Amorim</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583996907593</v>
+        <v>5522981585707</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Claudio</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Claudio Gabriel Santos</t>
+          <t>Diego de Souza Lourenço</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583986198745</v>
+        <v>5583987982658</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gustavo</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gustavo da Silva Santos</t>
+          <t>Maria de Fatima Nascimento de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583998652226</v>
+        <v>5583988865167</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Zaqueu</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Maria Stefany Brenda de Araujo</t>
+          <t>Zaqueu Ernesto da Silva</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583986677071</v>
+        <v>5583996825596</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Valquiria</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valquiria Pereira Gomes</t>
+          <t>Alex Bruno dos Santos Amaral</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5588994627581</v>
+        <v>5583996907593</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alefe</t>
+          <t>Claudio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alefe Batista Correia</t>
+          <t>Claudio Gabriel Santos</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583998093131</v>
+        <v>5583986198745</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Gustavo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jorge Tiner Silva</t>
+          <t>Gustavo da Silva Santos</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583996202501</v>
+        <v>5583998652226</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jesonnyas</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jesonnyas Fernandes de Souza Barbosa</t>
+          <t>Maria Stefany Brenda de Araujo</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583988562680</v>
+        <v>5583986677071</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valquiria</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Everton Luiz de Miranda Marques</t>
+          <t>Valquiria Pereira Gomes</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5511950902337</v>
+        <v>5588994627581</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Erinaldo</t>
+          <t>Alefe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Erinaldo Coreeia da Silva</t>
+          <t>Alefe Batista Correia</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583994051871</v>
+        <v>5583998093131</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Maria Jose Felipe dos Santos</t>
+          <t>Jorge Tiner Silva</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583993985820</v>
+        <v>5583996202501</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Silvan</t>
+          <t>Jesonnyas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Silvan Carlos Soares Ferreira</t>
+          <t>Jesonnyas Fernandes de Souza Barbosa</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583988589736</v>
+        <v>5583988562680</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adeilma</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Adeilma Clementino da Silva</t>
+          <t>Everton Luiz de Miranda Marques</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583988904044</v>
+        <v>5511950902337</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Erinaldo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jose Anulino Filho</t>
+          <t>Erinaldo Coreeia da Silva</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583999860041</v>
+        <v>5583994051871</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -993,232 +993,232 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Maria da Conceicao Ribeiro Silva</t>
+          <t>Maria Jose Felipe dos Santos</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5511947298657</v>
+        <v>5583993985820</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Silvan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ivan Araujo de Almeida</t>
+          <t>Silvan Carlos Soares Ferreira</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583988628374</v>
+        <v>5583988589736</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Adeilma</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jose Bezerra Matins</t>
+          <t>Adeilma Clementino da Silva</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583998637662</v>
+        <v>5583988904044</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gabriel Gomes Geriz</t>
+          <t>Jose Anulino Filho</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583982257636</v>
+        <v>5583999860041</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Atacadao</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atacadao Farias</t>
+          <t>Maria da Conceicao Ribeiro Silva</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583996442120</v>
+        <v>5511947298657</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maria Aparecida Rodrigues Ferreira</t>
+          <t>Ivan Araujo de Almeida</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583991828059</v>
+        <v>5583988628374</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alan Jorge Silvestre de Almeida</t>
+          <t>Jose Bezerra Matins</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583996090650</v>
+        <v>5583998637662</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Felipe</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Felipe Araujo de Oliveira</t>
+          <t>Gabriel Gomes Geriz</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583996307228</v>
+        <v>5583982257636</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Isnalhe</t>
+          <t>Atacadao</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Isnalhe de Souza</t>
+          <t>Atacadao Farias</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583997082437</v>
+        <v>5583996442120</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thiago Pereira do Nascimento</t>
+          <t>Maria Aparecida Rodrigues Ferreira</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583987480419</v>
+        <v>5583991828059</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gilberto</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gilberto Alves de Oliveira</t>
+          <t>Alan Jorge Silvestre de Almeida</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583982258636</v>
+        <v>5583996090650</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Laercio</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Laercio Dias de Araujo</t>
+          <t>Felipe Araujo de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583986529174</v>
+        <v>5583996307228</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Valner</t>
+          <t>Isnalhe</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valner dos Santos Franca</t>
+          <t>Isnalhe de Souza</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583986248293</v>
+        <v>5583997082437</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Annelyne</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Annelyne Soares Barbosa</t>
+          <t>Thiago Pereira do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583993443192</v>
+        <v>5583987480419</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Edson</t>
+          <t>Gilberto</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Edson Bruno Lourenco de Melo</t>
+          <t>Gilberto Alves de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583988941535</v>
+        <v>5583982258636</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Laercio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Casa Amarela Gas e Agua</t>
+          <t>Laercio Dias de Araujo</t>
         </is>
       </c>
     </row>
